--- a/stats_report_ms.xlsx
+++ b/stats_report_ms.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristakraskura/Github_repositories/KK_etal_synthesis_fish_temp_scaling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAF8827-2B3A-1B4E-A745-A3B0B500EC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B58AB6-C28C-3148-854F-768844F74297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="620" windowWidth="28800" windowHeight="17380" activeTab="1" xr2:uid="{B3FBD4CA-75DB-D748-9A95-2029329DF2D8}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" activeTab="3" xr2:uid="{B3FBD4CA-75DB-D748-9A95-2029329DF2D8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Table 1 - main text" sheetId="4" r:id="rId1"/>
+    <sheet name="OUTDATED - pre Review" sheetId="1" r:id="rId2"/>
+    <sheet name="ecology models -REVIEW" sheetId="3" r:id="rId3"/>
+    <sheet name="OUTDATED - pre review2" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_Toc224551882" localSheetId="0">'Table 1 - main text'!$Q$22</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="86">
   <si>
     <t>var</t>
   </si>
@@ -265,6 +269,57 @@
   <si>
     <t>AS,RMR, MMR</t>
   </si>
+  <si>
+    <t xml:space="preserve">Lifes tages </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMR </t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Adults</t>
+  </si>
+  <si>
+    <t>Juveniles</t>
+  </si>
+  <si>
+    <t>lnBM</t>
+  </si>
+  <si>
+    <t>lnBM * T</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>OPTIMAL TEMPERATURES</t>
+  </si>
+  <si>
+    <t>0 ‘***’ 0.001 ‘**’ 0.01 ‘*’ 0.05 ‘.’</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WARM TEMPERATURES</t>
+  </si>
 </sst>
 </file>
 
@@ -273,7 +328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -367,6 +422,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -405,7 +485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -926,12 +1006,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1092,36 +1183,57 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -1456,6 +1568,1194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C214D5-A090-8C45-856F-84A9FA36570B}">
+  <dimension ref="B2:V31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="16.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="Q2" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="86"/>
+      <c r="S2" s="86"/>
+      <c r="T2" s="86"/>
+      <c r="U2" s="86"/>
+      <c r="V2" s="86"/>
+    </row>
+    <row r="3" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="80">
+        <v>0.78812930000000003</v>
+      </c>
+      <c r="E5" s="80">
+        <v>0.1140671</v>
+      </c>
+      <c r="F5" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="80">
+        <v>0.77948700000000004</v>
+      </c>
+      <c r="H5" s="80">
+        <v>0.29003099999999998</v>
+      </c>
+      <c r="I5" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="80">
+        <v>1.046613</v>
+      </c>
+      <c r="K5" s="80">
+        <v>2.5801000000000001E-2</v>
+      </c>
+      <c r="L5" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5" s="80">
+        <v>0.12845100000000001</v>
+      </c>
+      <c r="N5" s="80">
+        <v>2.6379E-2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q5" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="S5" s="84" t="str">
+        <f>_xlfn.CONCAT(ROUND(D5,3)," (", ROUND(E5,3), ") ", F5)</f>
+        <v>0.788 (0.114) ***</v>
+      </c>
+      <c r="T5" s="84" t="str">
+        <f>_xlfn.CONCAT(ROUND(G5,3)," (", ROUND(H5,3), ") ", I5)</f>
+        <v>0.779 (0.29) **</v>
+      </c>
+      <c r="U5" s="84" t="str">
+        <f>_xlfn.CONCAT(ROUND(J5,3)," (", ROUND(K5,3), ") ", L5)</f>
+        <v>1.047 (0.026) ***</v>
+      </c>
+      <c r="V5" s="84" t="str">
+        <f>_xlfn.CONCAT(ROUND(M5,3)," (", ROUND(N5,3), ") ", O5)</f>
+        <v>0.128 (0.026) ***</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="80">
+        <v>5.2964400000000002E-2</v>
+      </c>
+      <c r="E6" s="80">
+        <v>3.0068E-3</v>
+      </c>
+      <c r="F6" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="80">
+        <v>3.9604E-2</v>
+      </c>
+      <c r="H6" s="80">
+        <v>1.7570000000000001E-3</v>
+      </c>
+      <c r="I6" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="80">
+        <v>6.8745000000000001E-2</v>
+      </c>
+      <c r="K6" s="80">
+        <v>4.7949999999999998E-3</v>
+      </c>
+      <c r="L6" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M6" s="80">
+        <v>-5.13E-3</v>
+      </c>
+      <c r="N6" s="80">
+        <v>7.2620000000000002E-3</v>
+      </c>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="S6" s="84" t="str">
+        <f t="shared" ref="S6:S7" si="0">_xlfn.CONCAT(ROUND(D6,3)," (", ROUND(E6,3), ") ", F6)</f>
+        <v>0.053 (0.003) ***</v>
+      </c>
+      <c r="T6" s="84" t="str">
+        <f t="shared" ref="T6:T28" si="1">_xlfn.CONCAT(ROUND(G6,3)," (", ROUND(H6,3), ") ", I6)</f>
+        <v>0.04 (0.002) ***</v>
+      </c>
+      <c r="U6" s="84" t="str">
+        <f t="shared" ref="U6:U29" si="2">_xlfn.CONCAT(ROUND(J6,3)," (", ROUND(K6,3), ") ", L6)</f>
+        <v>0.069 (0.005) ***</v>
+      </c>
+      <c r="V6" s="84" t="str">
+        <f t="shared" ref="V6:V28" si="3">_xlfn.CONCAT(ROUND(M6,3)," (", ROUND(N6,3), ") ", O6)</f>
+        <v xml:space="preserve">-0.005 (0.007) </v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="80">
+        <v>3.4807000000000002E-3</v>
+      </c>
+      <c r="E7" s="80">
+        <v>8.9519999999999997E-4</v>
+      </c>
+      <c r="F7" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="80">
+        <v>-9.9220000000000003E-3</v>
+      </c>
+      <c r="K7" s="80">
+        <v>1.1919999999999999E-3</v>
+      </c>
+      <c r="L7" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" s="80">
+        <v>-6.2389999999999998E-3</v>
+      </c>
+      <c r="N7" s="80">
+        <v>1.2359999999999999E-3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="S7" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>0.003 (0.001) ***</v>
+      </c>
+      <c r="T7" s="84"/>
+      <c r="U7" s="85" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.01 (0.001) ***</v>
+      </c>
+      <c r="V7" s="85" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.006 (0.001) ***</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="P8" s="80"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="84"/>
+      <c r="T8" s="84"/>
+      <c r="U8" s="84"/>
+      <c r="V8" s="84"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9">
+        <v>0.81041099999999999</v>
+      </c>
+      <c r="E9">
+        <v>0.185973</v>
+      </c>
+      <c r="F9" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9">
+        <v>0.92496999999999996</v>
+      </c>
+      <c r="H9">
+        <v>0.302149</v>
+      </c>
+      <c r="I9" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9">
+        <v>1.1279950000000001</v>
+      </c>
+      <c r="K9">
+        <v>3.7483000000000002E-2</v>
+      </c>
+      <c r="L9" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9">
+        <v>0.14822579999999999</v>
+      </c>
+      <c r="N9">
+        <v>3.6132400000000002E-2</v>
+      </c>
+      <c r="O9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="R9" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="S9" s="84" t="str">
+        <f>_xlfn.CONCAT(ROUND(D9,3)," (", ROUND(E9,3), ") ", F9)</f>
+        <v>0.81 (0.186) ***</v>
+      </c>
+      <c r="T9" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.925 (0.302) **</v>
+      </c>
+      <c r="U9" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>1.128 (0.037) ***</v>
+      </c>
+      <c r="V9" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>0.148 (0.036) ***</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10">
+        <v>7.4990000000000001E-2</v>
+      </c>
+      <c r="E10">
+        <v>1.8649999999999999E-3</v>
+      </c>
+      <c r="F10" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10">
+        <v>7.2283E-2</v>
+      </c>
+      <c r="H10">
+        <v>5.1500000000000001E-3</v>
+      </c>
+      <c r="I10" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10">
+        <v>7.3440000000000005E-2</v>
+      </c>
+      <c r="K10">
+        <v>1.4163E-2</v>
+      </c>
+      <c r="L10" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10">
+        <v>-4.484E-4</v>
+      </c>
+      <c r="N10">
+        <v>2.2057199999999999E-2</v>
+      </c>
+      <c r="Q10" s="84"/>
+      <c r="R10" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="S10" s="84" t="str">
+        <f t="shared" ref="S10" si="4">_xlfn.CONCAT(ROUND(D10,3)," (", ROUND(E10,3), ") ", F10)</f>
+        <v>0.075 (0.002) ***</v>
+      </c>
+      <c r="T10" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.072 (0.005) ***</v>
+      </c>
+      <c r="U10" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>0.073 (0.014) ***</v>
+      </c>
+      <c r="V10" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">0 (0.022) </v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>-8.6540000000000002E-3</v>
+      </c>
+      <c r="H11">
+        <v>1.6299999999999999E-3</v>
+      </c>
+      <c r="I11" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11">
+        <v>-1.3854E-2</v>
+      </c>
+      <c r="K11">
+        <v>1.8990000000000001E-3</v>
+      </c>
+      <c r="L11" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11">
+        <v>-7.5893000000000002E-3</v>
+      </c>
+      <c r="N11">
+        <v>1.8418E-3</v>
+      </c>
+      <c r="O11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" s="84"/>
+      <c r="R11" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="S11" s="84"/>
+      <c r="T11" s="85" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.009 (0.002) ***</v>
+      </c>
+      <c r="U11" s="85" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.014 (0.002) ***</v>
+      </c>
+      <c r="V11" s="85" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.008 (0.002) ***</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="84"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13">
+        <v>0.82521199999999995</v>
+      </c>
+      <c r="E13">
+        <v>7.8182000000000001E-2</v>
+      </c>
+      <c r="F13" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13">
+        <v>0.87922999999999996</v>
+      </c>
+      <c r="H13">
+        <v>0.28789900000000002</v>
+      </c>
+      <c r="I13" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="80">
+        <v>1.0014689999999999</v>
+      </c>
+      <c r="K13">
+        <v>0.57242599999999999</v>
+      </c>
+      <c r="L13" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13">
+        <v>-2.2669000000000002E-2</v>
+      </c>
+      <c r="N13">
+        <v>2.0070000000000001E-2</v>
+      </c>
+      <c r="Q13" s="84" t="s">
+        <v>72</v>
+      </c>
+      <c r="R13" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="S13" s="84" t="str">
+        <f>_xlfn.CONCAT(ROUND(D13,3)," (", ROUND(E13,3), ") ", F13)</f>
+        <v>0.825 (0.078) ***</v>
+      </c>
+      <c r="T13" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.879 (0.288) **</v>
+      </c>
+      <c r="U13" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>1.001 (0.572) .</v>
+      </c>
+      <c r="V13" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">-0.023 (0.02) </v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14">
+        <v>5.3792E-2</v>
+      </c>
+      <c r="E14">
+        <v>2.222E-3</v>
+      </c>
+      <c r="F14" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14">
+        <v>6.5110000000000003E-3</v>
+      </c>
+      <c r="H14">
+        <v>5.6649999999999999E-3</v>
+      </c>
+      <c r="J14">
+        <v>3.1241999999999999E-2</v>
+      </c>
+      <c r="K14">
+        <v>5.2249999999999996E-3</v>
+      </c>
+      <c r="L14" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M14">
+        <v>-3.1705999999999998E-2</v>
+      </c>
+      <c r="N14">
+        <v>5.5950000000000001E-3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="S14" s="84" t="str">
+        <f t="shared" ref="S14" si="5">_xlfn.CONCAT(ROUND(D14,3)," (", ROUND(E14,3), ") ", F14)</f>
+        <v>0.054 (0.002) ***</v>
+      </c>
+      <c r="T14" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">0.007 (0.006) </v>
+      </c>
+      <c r="U14" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>0.031 (0.005) ***</v>
+      </c>
+      <c r="V14" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.032 (0.006) ***</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>4.9399999999999999E-3</v>
+      </c>
+      <c r="H15">
+        <v>1.168E-3</v>
+      </c>
+      <c r="I15" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="S15" s="84"/>
+      <c r="T15" s="85" t="str">
+        <f t="shared" si="1"/>
+        <v>0.005 (0.001) ***</v>
+      </c>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+    </row>
+    <row r="16" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" s="86"/>
+      <c r="S16" s="86"/>
+      <c r="T16" s="86"/>
+      <c r="U16" s="86"/>
+      <c r="V16" s="86"/>
+    </row>
+    <row r="17" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="R17" s="82"/>
+      <c r="S17" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="T17" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="U17" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="P18" s="80"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="83"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="83"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="80">
+        <v>0.87666100000000002</v>
+      </c>
+      <c r="E19" s="80">
+        <v>1.6428999999999999E-2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="80">
+        <v>1.057698</v>
+      </c>
+      <c r="H19" s="80">
+        <v>3.5608000000000001E-2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19">
+        <v>1.1774290000000001</v>
+      </c>
+      <c r="K19">
+        <v>8.6161000000000001E-2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>82</v>
+      </c>
+      <c r="M19">
+        <v>-6.8898000000000001E-2</v>
+      </c>
+      <c r="N19">
+        <v>1.9102999999999998E-2</v>
+      </c>
+      <c r="O19" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="R19" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="S19" s="84" t="str">
+        <f t="shared" ref="S19:S28" si="6">_xlfn.CONCAT(ROUND(D19,3)," (", ROUND(E19,3), ") ", F19)</f>
+        <v>0.877 (0.016) ***</v>
+      </c>
+      <c r="T19" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>1.058 (0.036) ***</v>
+      </c>
+      <c r="U19" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>1.177 (0.086) ***</v>
+      </c>
+      <c r="V19" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.069 (0.019) ***</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="80">
+        <v>7.3394000000000001E-2</v>
+      </c>
+      <c r="E20" s="80">
+        <v>6.5240000000000003E-3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="80">
+        <v>3.9094999999999998E-2</v>
+      </c>
+      <c r="H20" s="80">
+        <v>1.3107000000000001E-2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20">
+        <v>5.731E-3</v>
+      </c>
+      <c r="K20">
+        <v>3.1213000000000001E-2</v>
+      </c>
+      <c r="M20">
+        <v>-4.5564E-2</v>
+      </c>
+      <c r="N20">
+        <v>2.0669999999999998E-3</v>
+      </c>
+      <c r="O20" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="S20" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>0.073 (0.007) ***</v>
+      </c>
+      <c r="T20" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.039 (0.013) **</v>
+      </c>
+      <c r="U20" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">0.006 (0.031) </v>
+      </c>
+      <c r="V20" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.046 (0.002) ***</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="80">
+        <v>-8.1899999999999994E-3</v>
+      </c>
+      <c r="H21" s="80">
+        <v>1.3339999999999999E-3</v>
+      </c>
+      <c r="I21" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21">
+        <v>-1.3981E-2</v>
+      </c>
+      <c r="K21">
+        <v>3.0730000000000002E-3</v>
+      </c>
+      <c r="L21" t="s">
+        <v>82</v>
+      </c>
+      <c r="M21" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="S21" s="84"/>
+      <c r="T21" s="85" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.008 (0.001) ***</v>
+      </c>
+      <c r="U21" s="85" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.014 (0.003) ***</v>
+      </c>
+      <c r="V21" s="84"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="P22" s="80"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="84"/>
+      <c r="V22" s="84"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23">
+        <v>0.82272199999999995</v>
+      </c>
+      <c r="E23">
+        <v>2.0414999999999999E-2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23">
+        <v>0.75630900000000001</v>
+      </c>
+      <c r="H23">
+        <v>0.168297</v>
+      </c>
+      <c r="I23" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23">
+        <v>0.79007000000000005</v>
+      </c>
+      <c r="K23">
+        <v>2.734E-2</v>
+      </c>
+      <c r="L23" t="s">
+        <v>82</v>
+      </c>
+      <c r="M23">
+        <v>-3.2555000000000001E-2</v>
+      </c>
+      <c r="N23">
+        <v>2.2006000000000001E-2</v>
+      </c>
+      <c r="Q23" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="R23" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="S23" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>0.823 (0.02) ***</v>
+      </c>
+      <c r="T23" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.756 (0.168) ***</v>
+      </c>
+      <c r="U23" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>0.79 (0.027) ***</v>
+      </c>
+      <c r="V23" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">-0.033 (0.022) </v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24">
+        <v>6.7450999999999997E-2</v>
+      </c>
+      <c r="E24">
+        <v>9.214E-3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24">
+        <v>3.8979E-2</v>
+      </c>
+      <c r="H24">
+        <v>1.389E-3</v>
+      </c>
+      <c r="I24" t="s">
+        <v>82</v>
+      </c>
+      <c r="J24">
+        <v>-1.8319999999999999E-2</v>
+      </c>
+      <c r="K24">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="M24">
+        <v>-3.8182000000000001E-2</v>
+      </c>
+      <c r="N24">
+        <v>6.1079999999999997E-3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q24" s="84"/>
+      <c r="R24" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="S24" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>0.067 (0.009) ***</v>
+      </c>
+      <c r="T24" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.039 (0.001) ***</v>
+      </c>
+      <c r="U24" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">-0.018 (0.027) </v>
+      </c>
+      <c r="V24" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.038 (0.006) ***</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="S25" s="84"/>
+      <c r="T25" s="84"/>
+      <c r="U25" s="84"/>
+      <c r="V25" s="84"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="Q26" s="84"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="84"/>
+      <c r="T26" s="84"/>
+      <c r="U26" s="84"/>
+      <c r="V26" s="84"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27">
+        <v>0.80867199999999995</v>
+      </c>
+      <c r="E27">
+        <v>2.9786E-2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27">
+        <v>0.84434699999999996</v>
+      </c>
+      <c r="H27">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>82</v>
+      </c>
+      <c r="J27">
+        <v>1.564057</v>
+      </c>
+      <c r="K27">
+        <v>0.190414</v>
+      </c>
+      <c r="L27" t="s">
+        <v>82</v>
+      </c>
+      <c r="M27">
+        <v>-0.16409000000000001</v>
+      </c>
+      <c r="N27">
+        <v>2.1319999999999999E-2</v>
+      </c>
+      <c r="O27" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q27" s="84" t="s">
+        <v>72</v>
+      </c>
+      <c r="R27" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="S27" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>0.809 (0.03) ***</v>
+      </c>
+      <c r="T27" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>0.844 (0.022) ***</v>
+      </c>
+      <c r="U27" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v>1.564 (0.19) ***</v>
+      </c>
+      <c r="V27" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.164 (0.021) ***</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28">
+        <v>8.1128000000000006E-2</v>
+      </c>
+      <c r="E28">
+        <v>8.9910000000000007E-3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28">
+        <v>-1.7402999999999998E-2</v>
+      </c>
+      <c r="H28">
+        <v>7.8139999999999998E-3</v>
+      </c>
+      <c r="I28" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28">
+        <v>4.0689999999999997E-2</v>
+      </c>
+      <c r="K28">
+        <v>3.7818999999999998E-2</v>
+      </c>
+      <c r="M28">
+        <v>-9.4759999999999997E-2</v>
+      </c>
+      <c r="N28">
+        <v>1.0880000000000001E-2</v>
+      </c>
+      <c r="O28" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="S28" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>0.081 (0.009) ***</v>
+      </c>
+      <c r="T28" s="84" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.017 (0.008) *</v>
+      </c>
+      <c r="U28" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">0.041 (0.038) </v>
+      </c>
+      <c r="V28" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.095 (0.011) ***</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29">
+        <v>-2.6235000000000001E-2</v>
+      </c>
+      <c r="K29">
+        <v>6.4279999999999997E-3</v>
+      </c>
+      <c r="L29" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q29" s="84"/>
+      <c r="R29" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="S29" s="84"/>
+      <c r="T29" s="84"/>
+      <c r="U29" s="85" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.026 (0.006) ***</v>
+      </c>
+      <c r="V29" s="84"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B16:N16"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="Q16:V16"/>
+    <mergeCell ref="Q2:V2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{422BEEAF-56E5-8347-860E-C228CBA812A8}">
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1494,13 +2794,13 @@
       <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="69" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="32" t="s">
@@ -1523,9 +2823,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="67"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="33" t="s">
         <v>49</v>
       </c>
@@ -1550,9 +2850,9 @@
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="67"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="70"/>
       <c r="D4" s="35" t="s">
         <v>62</v>
       </c>
@@ -1579,13 +2879,13 @@
       </c>
     </row>
     <row r="5" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="70" t="s">
         <v>63</v>
       </c>
       <c r="D5" s="36" t="s">
@@ -1612,9 +2912,9 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="70"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="67"/>
+      <c r="A6" s="73"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="70"/>
       <c r="D6" s="33" t="s">
         <v>6</v>
       </c>
@@ -1639,9 +2939,9 @@
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="71"/>
-      <c r="C7" s="67"/>
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="70"/>
       <c r="D7" s="35" t="s">
         <v>62</v>
       </c>
@@ -1666,13 +2966,13 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="67"/>
+      <c r="C8" s="70"/>
       <c r="D8" s="36" t="s">
         <v>50</v>
       </c>
@@ -1690,9 +2990,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="67"/>
+      <c r="A9" s="73"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="70"/>
       <c r="D9" s="33" t="s">
         <v>6</v>
       </c>
@@ -1710,9 +3010,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="67"/>
+      <c r="A10" s="73"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="70"/>
       <c r="D10" s="35" t="s">
         <v>62</v>
       </c>
@@ -1730,11 +3030,11 @@
       </c>
     </row>
     <row r="11" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="67"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="70"/>
       <c r="D11" s="36" t="s">
         <v>50</v>
       </c>
@@ -1752,9 +3052,9 @@
       </c>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="67"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="70"/>
       <c r="D12" s="33" t="s">
         <v>6</v>
       </c>
@@ -1772,9 +3072,9 @@
       </c>
     </row>
     <row r="13" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="67"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="70"/>
       <c r="D13" s="35" t="s">
         <v>62</v>
       </c>
@@ -1792,11 +3092,11 @@
       </c>
     </row>
     <row r="14" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="67"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="70"/>
       <c r="D14" s="36" t="s">
         <v>50</v>
       </c>
@@ -1814,9 +3114,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="70"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="67"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="70"/>
       <c r="D15" s="33" t="s">
         <v>6</v>
       </c>
@@ -1834,9 +3134,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="70"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="67"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="35" t="s">
         <v>62</v>
       </c>
@@ -1854,11 +3154,11 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="67"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="36" t="s">
         <v>50</v>
       </c>
@@ -1876,9 +3176,9 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="67"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="33" t="s">
         <v>6</v>
       </c>
@@ -1896,9 +3196,9 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="70"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="67"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="70"/>
       <c r="D19" s="35" t="s">
         <v>62</v>
       </c>
@@ -1916,13 +3216,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="67"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="36" t="s">
         <v>50</v>
       </c>
@@ -1940,9 +3240,9 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="70"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="67"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="33" t="s">
         <v>6</v>
       </c>
@@ -1960,9 +3260,9 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="70"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="67"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="70"/>
       <c r="D22" s="33" t="s">
         <v>62</v>
       </c>
@@ -1980,9 +3280,9 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="70"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="67"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="70"/>
       <c r="D23" s="37" t="s">
         <v>14</v>
       </c>
@@ -2000,11 +3300,11 @@
       </c>
     </row>
     <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="67"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="70"/>
       <c r="D24" s="32" t="s">
         <v>50</v>
       </c>
@@ -2022,9 +3322,9 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="70"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="67"/>
+      <c r="A25" s="73"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="70"/>
       <c r="D25" s="33" t="s">
         <v>6</v>
       </c>
@@ -2042,9 +3342,9 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="70"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="67"/>
+      <c r="A26" s="73"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="70"/>
       <c r="D26" s="34" t="s">
         <v>62</v>
       </c>
@@ -2062,9 +3362,9 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="67"/>
+      <c r="A27" s="73"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="70"/>
       <c r="D27" s="35" t="s">
         <v>14</v>
       </c>
@@ -2082,11 +3382,11 @@
       </c>
     </row>
     <row r="28" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="67"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="70"/>
       <c r="D28" s="32" t="s">
         <v>50</v>
       </c>
@@ -2104,9 +3404,9 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="70"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="67"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="70"/>
       <c r="D29" s="33" t="s">
         <v>6</v>
       </c>
@@ -2124,9 +3424,9 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="70"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="67"/>
+      <c r="A30" s="73"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="70"/>
       <c r="D30" s="33" t="s">
         <v>62</v>
       </c>
@@ -2144,9 +3444,9 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="70"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="67"/>
+      <c r="A31" s="73"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="70"/>
       <c r="D31" s="35" t="s">
         <v>14</v>
       </c>
@@ -2164,11 +3464,11 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="71"/>
-      <c r="C32" s="67"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="70"/>
       <c r="D32" s="32" t="s">
         <v>50</v>
       </c>
@@ -2186,9 +3486,9 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="70"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="67"/>
+      <c r="A33" s="73"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="70"/>
       <c r="D33" s="33" t="s">
         <v>6</v>
       </c>
@@ -2206,9 +3506,9 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="70"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="67"/>
+      <c r="A34" s="73"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="70"/>
       <c r="D34" s="33" t="s">
         <v>62</v>
       </c>
@@ -2226,9 +3526,9 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="74"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="68"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="71"/>
       <c r="D35" s="35" t="s">
         <v>14</v>
       </c>
@@ -2268,7 +3568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD51559-BDF0-9B49-9ED9-E6A711315C29}">
   <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2625,7 +3925,7 @@
       <c r="B12" s="4">
         <v>980.17748153122</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="66">
         <v>0</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -2655,7 +3955,7 @@
       <c r="B13" s="5">
         <v>980.35033275221303</v>
       </c>
-      <c r="C13" s="76">
+      <c r="C13" s="67">
         <v>0.17285</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -2800,7 +4100,7 @@
       <c r="B18" s="4">
         <v>1306.57011590707</v>
       </c>
-      <c r="C18" s="75">
+      <c r="C18" s="66">
         <v>0</v>
       </c>
       <c r="D18" s="56" t="s">
@@ -2823,7 +4123,7 @@
       <c r="B19" s="5">
         <v>1307.62016643065</v>
       </c>
-      <c r="C19" s="76">
+      <c r="C19" s="67">
         <v>1.0500499999999999</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -2846,7 +4146,7 @@
       <c r="B20" s="4">
         <v>1304.2954624496199</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="66">
         <v>0</v>
       </c>
       <c r="D20" s="56" t="s">
@@ -2869,7 +4169,7 @@
       <c r="B21" s="5">
         <v>1307.62016643065</v>
       </c>
-      <c r="C21" s="76">
+      <c r="C21" s="67">
         <v>3.3247</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -2892,7 +4192,7 @@
       <c r="B22" s="4">
         <v>1302.2470979355101</v>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="66">
         <v>0</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -2915,7 +4215,7 @@
       <c r="B23" s="5">
         <v>1307.62016643065</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="67">
         <v>5.3730700000000002</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -3171,7 +4471,7 @@
       <c r="C34" s="58">
         <v>0</v>
       </c>
-      <c r="D34" s="77" t="s">
+      <c r="D34" s="68" t="s">
         <v>41</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -3306,10 +4606,10 @@
       <c r="B40" s="4">
         <v>1800.40438010912</v>
       </c>
-      <c r="C40" s="75">
+      <c r="C40" s="66">
         <v>0</v>
       </c>
-      <c r="D40" s="77" t="s">
+      <c r="D40" s="68" t="s">
         <v>41</v>
       </c>
       <c r="E40" s="4" t="s">
@@ -3329,7 +4629,7 @@
       <c r="B41" s="5">
         <v>1800.61415122567</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="67">
         <v>0.20977000000000001</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -3628,7 +4928,7 @@
       <c r="B54" s="4">
         <v>-438.35695470056601</v>
       </c>
-      <c r="C54" s="75">
+      <c r="C54" s="66">
         <v>0</v>
       </c>
       <c r="D54" s="4" t="s">
@@ -3651,7 +4951,7 @@
       <c r="B55" s="5">
         <v>-431.77489630451402</v>
       </c>
-      <c r="C55" s="76">
+      <c r="C55" s="67">
         <v>6.5820600000000002</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -3674,7 +4974,7 @@
       <c r="B56" s="4">
         <v>-435.96612865057801</v>
       </c>
-      <c r="C56" s="75">
+      <c r="C56" s="66">
         <v>0</v>
       </c>
       <c r="D56" s="4" t="s">
@@ -3697,7 +4997,7 @@
       <c r="B57" s="5">
         <v>-431.77489630451402</v>
       </c>
-      <c r="C57" s="76">
+      <c r="C57" s="67">
         <v>4.19123</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -3902,13 +5202,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBA0834-6EA2-3D4D-B386-80B68D11CC8F}">
   <dimension ref="B1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.1640625" bestFit="1" customWidth="1"/>
   </cols>

--- a/stats_report_ms.xlsx
+++ b/stats_report_ms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristakraskura/Github_repositories/KK_etal_synthesis_fish_temp_scaling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF6DAB6-E228-A643-8772-07F477F942E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D87F5-75A2-4C4D-BCC0-93B093AA3B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="620" windowWidth="28800" windowHeight="17380" activeTab="1" xr2:uid="{B3FBD4CA-75DB-D748-9A95-2029329DF2D8}"/>
+    <workbookView xWindow="720" yWindow="620" windowWidth="28800" windowHeight="17380" activeTab="4" xr2:uid="{B3FBD4CA-75DB-D748-9A95-2029329DF2D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1 - main text" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="317">
   <si>
     <t>var</t>
   </si>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>BICbut null not ∆BIC &gt; 7</t>
+  </si>
+  <si>
+    <t>reported</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1866,7 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2052,57 +2055,10 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
@@ -2133,6 +2089,45 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="20% - Accent6" xfId="3" builtinId="50"/>
@@ -2482,29 +2477,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="Q2" s="93" t="s">
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="Q2" s="129" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="93"/>
-      <c r="S2" s="93"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
     </row>
     <row r="3" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -3087,30 +3082,30 @@
       <c r="V15" s="63"/>
     </row>
     <row r="16" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="92" t="s">
+      <c r="B16" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="92"/>
-      <c r="D16" s="92"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="92"/>
-      <c r="K16" s="92"/>
-      <c r="L16" s="92"/>
-      <c r="M16" s="92"/>
-      <c r="N16" s="92"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
       <c r="P16" s="59"/>
-      <c r="Q16" s="93" t="s">
+      <c r="Q16" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="R16" s="93"/>
-      <c r="S16" s="93"/>
-      <c r="T16" s="93"/>
-      <c r="U16" s="93"/>
-      <c r="V16" s="93"/>
+      <c r="R16" s="129"/>
+      <c r="S16" s="129"/>
+      <c r="T16" s="129"/>
+      <c r="U16" s="129"/>
+      <c r="V16" s="129"/>
     </row>
     <row r="17" spans="2:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="58" t="s">
@@ -3651,14 +3646,14 @@
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B32" s="59"/>
-      <c r="F32" s="113"/>
+      <c r="F32" s="96"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="59"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="59"/>
-      <c r="F34" s="113"/>
+      <c r="F34" s="96"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="59"/>
@@ -3695,54 +3690,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
-      <c r="W1" s="95" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="126"/>
+      <c r="T1" s="126"/>
+      <c r="U1" s="126"/>
+      <c r="V1" s="126"/>
+      <c r="W1" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="95"/>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="95"/>
-      <c r="AC1" s="95"/>
-      <c r="AD1" s="95"/>
-      <c r="AE1" s="95"/>
-      <c r="AF1" s="95"/>
-      <c r="AG1" s="95"/>
-      <c r="AH1" s="95"/>
-      <c r="AI1" s="95"/>
-      <c r="AJ1" s="95"/>
-      <c r="AK1" s="95"/>
-      <c r="AL1" s="95"/>
-      <c r="AM1" s="95"/>
-      <c r="AN1" s="95"/>
-      <c r="AO1" s="95"/>
-      <c r="AP1" s="95"/>
-      <c r="AQ1" s="95"/>
-      <c r="AR1" s="95"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="127"/>
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
       <c r="AT1"/>
       <c r="AU1"/>
     </row>
@@ -3891,10 +3886,10 @@
       <c r="AW2" t="s">
         <v>219</v>
       </c>
-      <c r="AX2" s="92" t="s">
+      <c r="AX2" s="128" t="s">
         <v>313</v>
       </c>
-      <c r="AY2" s="92"/>
+      <c r="AY2" s="128"/>
     </row>
     <row r="3" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -4118,11 +4113,11 @@
       <c r="AU4" s="75">
         <v>1.18</v>
       </c>
-      <c r="AV4" s="129">
+      <c r="AV4" s="112">
         <f>AU4-AT4</f>
         <v>0.21999999999999997</v>
       </c>
-      <c r="AW4" s="130"/>
+      <c r="AW4" s="113"/>
       <c r="AX4" t="b">
         <f>C4&lt;C5</f>
         <v>1</v>
@@ -4274,8 +4269,8 @@
       <c r="AU5" s="75">
         <v>0.85</v>
       </c>
-      <c r="AV5" s="131"/>
-      <c r="AW5" s="132">
+      <c r="AV5" s="114"/>
+      <c r="AW5" s="115">
         <f>Y5-C5</f>
         <v>-0.15000000000000002</v>
       </c>
@@ -5026,11 +5021,11 @@
       <c r="AU10" s="75">
         <v>0.92</v>
       </c>
-      <c r="AV10" s="133">
+      <c r="AV10" s="116">
         <f>Y10-C10</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW10" s="134"/>
+      <c r="AW10" s="117"/>
       <c r="AX10" t="b">
         <f>C10&lt;C11</f>
         <v>1</v>
@@ -5182,8 +5177,8 @@
       <c r="AU11" s="75">
         <v>0.97</v>
       </c>
-      <c r="AV11" s="135"/>
-      <c r="AW11" s="136">
+      <c r="AV11" s="118"/>
+      <c r="AW11" s="119">
         <f>Y11-C11</f>
         <v>-2.0000000000000018E-2</v>
       </c>
@@ -6538,11 +6533,11 @@
       <c r="AU20" s="75">
         <v>0.78</v>
       </c>
-      <c r="AV20" s="128">
+      <c r="AV20" s="111">
         <f>Y20-C20</f>
         <v>-3.0000000000000027E-2</v>
       </c>
-      <c r="AW20" s="128"/>
+      <c r="AW20" s="111"/>
       <c r="AX20" t="b">
         <f>C20&lt;C21</f>
         <v>1</v>
@@ -6694,8 +6689,8 @@
       <c r="AU21" s="75">
         <v>0.84</v>
       </c>
-      <c r="AV21" s="128"/>
-      <c r="AW21" s="128">
+      <c r="AV21" s="111"/>
+      <c r="AW21" s="111">
         <f>Y21-C21</f>
         <v>-6.0000000000000053E-2</v>
       </c>
@@ -7912,306 +7907,306 @@
         <v>-0.51</v>
       </c>
     </row>
-    <row r="32" spans="1:51" s="138" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="138" t="s">
+    <row r="32" spans="1:51" s="121" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="121" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="138">
+      <c r="B32" s="121">
         <v>-3.72</v>
       </c>
-      <c r="C32" s="138">
+      <c r="C32" s="121">
         <v>0.97</v>
       </c>
-      <c r="D32" s="138">
+      <c r="D32" s="121">
         <v>0.06</v>
       </c>
-      <c r="E32" s="138">
+      <c r="E32" s="121">
         <v>-4.17</v>
       </c>
-      <c r="F32" s="138">
+      <c r="F32" s="121">
         <v>0.92</v>
       </c>
-      <c r="G32" s="138">
+      <c r="G32" s="121">
         <v>0.05</v>
       </c>
-      <c r="H32" s="138">
+      <c r="H32" s="121">
         <v>-3.27</v>
       </c>
-      <c r="I32" s="138">
+      <c r="I32" s="121">
         <v>1.01</v>
       </c>
-      <c r="J32" s="138">
+      <c r="J32" s="121">
         <v>0.08</v>
       </c>
-      <c r="K32" s="138" t="s">
+      <c r="K32" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="L32" s="138" t="s">
+      <c r="L32" s="121" t="s">
         <v>107</v>
       </c>
-      <c r="M32" s="138">
+      <c r="M32" s="121">
         <v>0.25</v>
       </c>
-      <c r="N32" s="138">
+      <c r="N32" s="121">
         <v>88</v>
       </c>
-      <c r="O32" s="138">
+      <c r="O32" s="121">
         <v>499</v>
       </c>
-      <c r="P32" s="138">
+      <c r="P32" s="121">
         <v>15</v>
       </c>
-      <c r="Q32" s="138">
+      <c r="Q32" s="121">
         <v>31</v>
       </c>
-      <c r="R32" s="138">
+      <c r="R32" s="121">
         <v>26</v>
       </c>
-      <c r="S32" s="138" t="s">
+      <c r="S32" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="T32" s="138" t="s">
+      <c r="T32" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="U32" s="138" t="s">
+      <c r="U32" s="121" t="s">
         <v>160</v>
       </c>
-      <c r="V32" s="139">
-        <v>1</v>
-      </c>
-      <c r="W32" s="138" t="s">
+      <c r="V32" s="122">
+        <v>1</v>
+      </c>
+      <c r="W32" s="121" t="s">
         <v>158</v>
       </c>
-      <c r="X32" s="138">
+      <c r="X32" s="121">
         <v>0.27</v>
       </c>
-      <c r="Y32" s="138">
+      <c r="Y32" s="121">
         <v>1.06</v>
       </c>
-      <c r="Z32" s="138">
+      <c r="Z32" s="121">
         <v>-0.04</v>
       </c>
-      <c r="AA32" s="138">
+      <c r="AA32" s="121">
         <v>-0.52</v>
       </c>
-      <c r="AB32" s="138">
+      <c r="AB32" s="121">
         <v>1.01</v>
       </c>
-      <c r="AC32" s="138">
+      <c r="AC32" s="121">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="AD32" s="138">
+      <c r="AD32" s="121">
         <v>1.06</v>
       </c>
-      <c r="AE32" s="138">
+      <c r="AE32" s="121">
         <v>1.1200000000000001</v>
       </c>
-      <c r="AF32" s="138">
+      <c r="AF32" s="121">
         <v>0</v>
       </c>
-      <c r="AG32" s="138" t="s">
+      <c r="AG32" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="AH32" s="138" t="s">
+      <c r="AH32" s="121" t="s">
         <v>107</v>
       </c>
-      <c r="AI32" s="138">
+      <c r="AI32" s="121">
         <v>0.45</v>
       </c>
-      <c r="AJ32" s="138">
+      <c r="AJ32" s="121">
         <v>119</v>
       </c>
-      <c r="AK32" s="138">
+      <c r="AK32" s="121">
         <v>315</v>
       </c>
-      <c r="AL32" s="138">
+      <c r="AL32" s="121">
         <v>25</v>
       </c>
-      <c r="AM32" s="138">
+      <c r="AM32" s="121">
         <v>31</v>
       </c>
-      <c r="AN32" s="138">
+      <c r="AN32" s="121">
         <v>25</v>
       </c>
-      <c r="AO32" s="138" t="s">
+      <c r="AO32" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="AP32" s="138" t="s">
+      <c r="AP32" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="AQ32" s="138" t="s">
+      <c r="AQ32" s="121" t="s">
         <v>204</v>
       </c>
-      <c r="AR32" s="138">
-        <v>1</v>
-      </c>
-      <c r="AS32" s="140" t="s">
+      <c r="AR32" s="121">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="123" t="s">
         <v>158</v>
       </c>
-      <c r="AT32" s="138">
+      <c r="AT32" s="121">
         <v>0.97</v>
       </c>
-      <c r="AU32" s="138">
+      <c r="AU32" s="121">
         <v>1.06</v>
       </c>
-      <c r="AV32" s="141">
+      <c r="AV32" s="124">
         <f>AU32-AT32</f>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AW32" s="141"/>
-      <c r="AX32" s="142" t="b">
+      <c r="AW32" s="124"/>
+      <c r="AX32" s="125" t="b">
         <f>C32&lt;C33</f>
         <v>0</v>
       </c>
-      <c r="AY32" s="142" t="b">
+      <c r="AY32" s="125" t="b">
         <f>Y32&lt;Y33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:51" s="138" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="138" t="s">
+    <row r="33" spans="1:51" s="121" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="121" t="s">
         <v>161</v>
       </c>
-      <c r="B33" s="138">
+      <c r="B33" s="121">
         <v>-0.89</v>
       </c>
-      <c r="C33" s="138">
+      <c r="C33" s="121">
         <v>0.76</v>
       </c>
-      <c r="D33" s="138">
+      <c r="D33" s="121">
         <v>0.01</v>
       </c>
-      <c r="E33" s="138">
+      <c r="E33" s="121">
         <v>-1.99</v>
       </c>
-      <c r="F33" s="138">
+      <c r="F33" s="121">
         <v>0.7</v>
       </c>
-      <c r="G33" s="138">
+      <c r="G33" s="121">
         <v>-0.02</v>
       </c>
-      <c r="H33" s="138">
+      <c r="H33" s="121">
         <v>0.2</v>
       </c>
-      <c r="I33" s="138">
+      <c r="I33" s="121">
         <v>0.82</v>
       </c>
-      <c r="J33" s="138">
+      <c r="J33" s="121">
         <v>0.05</v>
       </c>
-      <c r="K33" s="138" t="s">
+      <c r="K33" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="L33" s="138" t="s">
+      <c r="L33" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="138">
+      <c r="M33" s="121">
         <v>0.97</v>
       </c>
-      <c r="N33" s="138">
+      <c r="N33" s="121">
         <v>50.08</v>
       </c>
-      <c r="O33" s="138">
+      <c r="O33" s="121">
         <v>55</v>
       </c>
-      <c r="P33" s="138">
+      <c r="P33" s="121">
         <v>30</v>
       </c>
-      <c r="Q33" s="138">
+      <c r="Q33" s="121">
         <v>35</v>
       </c>
-      <c r="R33" s="138">
+      <c r="R33" s="121">
         <v>2</v>
       </c>
-      <c r="S33" s="138" t="s">
+      <c r="S33" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="T33" s="138" t="s">
+      <c r="T33" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="U33" s="138" t="s">
+      <c r="U33" s="121" t="s">
         <v>162</v>
       </c>
-      <c r="V33" s="139">
+      <c r="V33" s="122">
         <v>0</v>
       </c>
-      <c r="W33" s="138" t="s">
+      <c r="W33" s="121" t="s">
         <v>161</v>
       </c>
-      <c r="X33" s="138">
+      <c r="X33" s="121">
         <v>-0.97</v>
       </c>
-      <c r="Y33" s="138">
+      <c r="Y33" s="121">
         <v>0.77</v>
       </c>
-      <c r="Z33" s="138">
+      <c r="Z33" s="121">
         <v>0.05</v>
       </c>
-      <c r="AA33" s="138">
+      <c r="AA33" s="121">
         <v>-1.65</v>
       </c>
-      <c r="AB33" s="138">
+      <c r="AB33" s="121">
         <v>0.71</v>
       </c>
-      <c r="AC33" s="138">
+      <c r="AC33" s="121">
         <v>0.03</v>
       </c>
-      <c r="AD33" s="138">
+      <c r="AD33" s="121">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="AE33" s="138">
+      <c r="AE33" s="121">
         <v>0.84</v>
       </c>
-      <c r="AF33" s="138">
+      <c r="AF33" s="121">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AG33" s="138" t="s">
+      <c r="AG33" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="AH33" s="138" t="s">
+      <c r="AH33" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="AI33" s="138">
+      <c r="AI33" s="121">
         <v>4.62</v>
       </c>
-      <c r="AJ33" s="138">
+      <c r="AJ33" s="121">
         <v>119</v>
       </c>
-      <c r="AK33" s="138">
+      <c r="AK33" s="121">
         <v>55</v>
       </c>
-      <c r="AL33" s="138">
+      <c r="AL33" s="121">
         <v>31</v>
       </c>
-      <c r="AM33" s="138">
+      <c r="AM33" s="121">
         <v>39</v>
       </c>
-      <c r="AN33" s="138">
+      <c r="AN33" s="121">
         <v>2</v>
       </c>
-      <c r="AO33" s="138" t="s">
+      <c r="AO33" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="AP33" s="138" t="s">
+      <c r="AP33" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="AQ33" s="138" t="s">
+      <c r="AQ33" s="121" t="s">
         <v>162</v>
       </c>
-      <c r="AR33" s="138">
+      <c r="AR33" s="121">
         <v>0</v>
       </c>
-      <c r="AS33" s="140" t="s">
+      <c r="AS33" s="123" t="s">
         <v>161</v>
       </c>
-      <c r="AT33" s="138">
+      <c r="AT33" s="121">
         <v>0.76</v>
       </c>
-      <c r="AU33" s="138">
+      <c r="AU33" s="121">
         <v>0.77</v>
       </c>
-      <c r="AV33" s="141"/>
-      <c r="AW33" s="141">
+      <c r="AV33" s="124"/>
+      <c r="AW33" s="124">
         <f>AU33-AT33</f>
         <v>1.0000000000000009E-2</v>
       </c>
@@ -8962,11 +8957,11 @@
       <c r="A2" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124">
+      <c r="B2" s="106"/>
+      <c r="C2" s="107">
         <v>0.69</v>
       </c>
-      <c r="D2" s="125">
+      <c r="D2" s="108">
         <v>0.05</v>
       </c>
       <c r="E2" s="80">
@@ -9031,14 +9026,14 @@
       <c r="A3" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="126" t="b">
+      <c r="B3" s="109" t="b">
         <f>D3&lt;D2</f>
         <v>1</v>
       </c>
       <c r="C3" s="81">
         <v>1.75</v>
       </c>
-      <c r="D3" s="127">
+      <c r="D3" s="110">
         <v>-0.25</v>
       </c>
       <c r="E3" s="80">
@@ -9244,11 +9239,11 @@
       <c r="A6" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="124">
+      <c r="B6" s="106"/>
+      <c r="C6" s="107">
         <v>2.71</v>
       </c>
-      <c r="D6" s="125">
+      <c r="D6" s="108">
         <v>-0.04</v>
       </c>
       <c r="E6" s="80">
@@ -9313,14 +9308,14 @@
       <c r="A7" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="126" t="b">
+      <c r="B7" s="109" t="b">
         <f>D7&lt;D6</f>
         <v>1</v>
       </c>
       <c r="C7" s="81">
         <v>5.85</v>
       </c>
-      <c r="D7" s="127">
+      <c r="D7" s="110">
         <v>-0.31</v>
       </c>
       <c r="E7" s="80">
@@ -10549,76 +10544,60 @@
       <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="105">
+      <c r="A2" s="92">
         <v>11</v>
       </c>
-      <c r="B2" s="105">
+      <c r="B2" s="92">
         <v>978.26477833776005</v>
       </c>
-      <c r="C2" s="105">
+      <c r="C2" s="92">
         <v>0</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="D2" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="105" t="s">
+      <c r="E2" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="105" t="s">
+      <c r="F2" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="105" t="s">
+      <c r="G2" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
     </row>
     <row r="3" spans="1:16" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="106">
+      <c r="A3" s="93">
         <v>8</v>
       </c>
-      <c r="B3" s="106">
+      <c r="B3" s="93">
         <v>987.76119356706704</v>
       </c>
-      <c r="C3" s="106">
+      <c r="C3" s="93">
         <v>9.4964200000000005</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="106" t="s">
+      <c r="E3" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="106" t="s">
+      <c r="F3" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="106" t="s">
+      <c r="G3" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="110"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="109"/>
+      <c r="I3" s="95"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3" s="95"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -10642,14 +10621,10 @@
       <c r="G4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="109"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:16" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
@@ -10673,14 +10648,14 @@
       <c r="G5" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="109"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="112"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
+      <c r="I5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5"/>
+      <c r="P5"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -10704,14 +10679,10 @@
       <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="109"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:16" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
@@ -10735,14 +10706,14 @@
       <c r="G7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="109"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="109"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="109"/>
+      <c r="I7"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7"/>
+      <c r="P7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -10769,14 +10740,10 @@
       <c r="H8" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="109"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="109"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:16" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
@@ -10800,14 +10767,14 @@
       <c r="G9" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="109"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="109"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -11128,48 +11095,48 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="105">
+      <c r="A22" s="92">
         <v>11</v>
       </c>
-      <c r="B22" s="105">
+      <c r="B22" s="92">
         <v>792.34289166193798</v>
       </c>
-      <c r="C22" s="105">
+      <c r="C22" s="92">
         <v>0</v>
       </c>
-      <c r="D22" s="105" t="s">
+      <c r="D22" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="105" t="s">
+      <c r="E22" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="105" t="s">
+      <c r="F22" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="105" t="s">
+      <c r="G22" s="92" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="106">
+      <c r="A23" s="93">
         <v>8</v>
       </c>
-      <c r="B23" s="106">
+      <c r="B23" s="93">
         <v>800.14058176603498</v>
       </c>
-      <c r="C23" s="106">
+      <c r="C23" s="93">
         <v>7.7976900000000002</v>
       </c>
-      <c r="D23" s="106" t="s">
+      <c r="D23" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="106" t="s">
+      <c r="E23" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="106" t="s">
+      <c r="F23" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G23" s="106" t="s">
+      <c r="G23" s="93" t="s">
         <v>8</v>
       </c>
     </row>
@@ -11404,186 +11371,186 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="105">
+      <c r="A34" s="92">
         <v>11</v>
       </c>
-      <c r="B34" s="105">
+      <c r="B34" s="92">
         <v>1222.2301565796499</v>
       </c>
-      <c r="C34" s="105">
+      <c r="C34" s="92">
         <v>0</v>
       </c>
-      <c r="D34" s="105" t="s">
+      <c r="D34" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="105" t="s">
+      <c r="E34" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="105" t="s">
+      <c r="F34" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G34" s="105" t="s">
+      <c r="G34" s="92" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="106">
+      <c r="A35" s="93">
         <v>8</v>
       </c>
-      <c r="B35" s="106">
+      <c r="B35" s="93">
         <v>1238.04595344469</v>
       </c>
-      <c r="C35" s="106">
+      <c r="C35" s="93">
         <v>15.815799999999999</v>
       </c>
-      <c r="D35" s="106" t="s">
+      <c r="D35" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="106" t="s">
+      <c r="E35" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="106" t="s">
+      <c r="F35" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G35" s="106" t="s">
+      <c r="G35" s="93" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="105">
+      <c r="A36" s="92">
         <v>11</v>
       </c>
-      <c r="B36" s="105">
+      <c r="B36" s="92">
         <v>1211.0200161218499</v>
       </c>
-      <c r="C36" s="105">
+      <c r="C36" s="92">
         <v>0</v>
       </c>
-      <c r="D36" s="105" t="s">
+      <c r="D36" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E36" s="105" t="s">
+      <c r="E36" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="105" t="s">
+      <c r="F36" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G36" s="105" t="s">
+      <c r="G36" s="92" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="106">
+      <c r="A37" s="93">
         <v>8</v>
       </c>
-      <c r="B37" s="106">
+      <c r="B37" s="93">
         <v>1238.04595344469</v>
       </c>
-      <c r="C37" s="106">
+      <c r="C37" s="93">
         <v>27.025939999999999</v>
       </c>
-      <c r="D37" s="106" t="s">
+      <c r="D37" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E37" s="106" t="s">
+      <c r="E37" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="106" t="s">
+      <c r="F37" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G37" s="106" t="s">
+      <c r="G37" s="93" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="105">
+      <c r="A38" s="92">
         <v>11</v>
       </c>
-      <c r="B38" s="105">
+      <c r="B38" s="92">
         <v>1216.21478985304</v>
       </c>
-      <c r="C38" s="105">
+      <c r="C38" s="92">
         <v>0</v>
       </c>
-      <c r="D38" s="105" t="s">
+      <c r="D38" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="105" t="s">
+      <c r="E38" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="105" t="s">
+      <c r="F38" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G38" s="105" t="s">
+      <c r="G38" s="92" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="106">
+      <c r="A39" s="93">
         <v>8</v>
       </c>
-      <c r="B39" s="106">
+      <c r="B39" s="93">
         <v>1238.04595344469</v>
       </c>
-      <c r="C39" s="106">
+      <c r="C39" s="93">
         <v>21.831160000000001</v>
       </c>
-      <c r="D39" s="106" t="s">
+      <c r="D39" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="106" t="s">
+      <c r="E39" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="106" t="s">
+      <c r="F39" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="106" t="s">
+      <c r="G39" s="93" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="105">
+      <c r="A40" s="92">
         <v>12</v>
       </c>
-      <c r="B40" s="105">
+      <c r="B40" s="92">
         <v>1230.1346857926601</v>
       </c>
-      <c r="C40" s="105">
+      <c r="C40" s="92">
         <v>0</v>
       </c>
-      <c r="D40" s="105" t="s">
+      <c r="D40" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="105" t="s">
+      <c r="E40" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="105" t="s">
+      <c r="F40" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G40" s="105" t="s">
+      <c r="G40" s="92" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="106">
+      <c r="A41" s="93">
         <v>8</v>
       </c>
-      <c r="B41" s="106">
+      <c r="B41" s="93">
         <v>1238.04595344469</v>
       </c>
-      <c r="C41" s="106">
+      <c r="C41" s="93">
         <v>7.91127</v>
       </c>
-      <c r="D41" s="106" t="s">
+      <c r="D41" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E41" s="106" t="s">
+      <c r="E41" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="106" t="s">
+      <c r="F41" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G41" s="106" t="s">
+      <c r="G41" s="93" t="s">
         <v>9</v>
       </c>
     </row>
@@ -11772,94 +11739,94 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="114">
+      <c r="A50" s="97">
         <v>10</v>
       </c>
-      <c r="B50" s="114">
+      <c r="B50" s="97">
         <v>-452.19948622983702</v>
       </c>
-      <c r="C50" s="114">
+      <c r="C50" s="97">
         <v>0</v>
       </c>
-      <c r="D50" s="114" t="s">
+      <c r="D50" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="114" t="s">
+      <c r="E50" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="114" t="s">
+      <c r="F50" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="G50" s="114" t="s">
+      <c r="G50" s="97" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="117">
+      <c r="A51" s="100">
         <v>7</v>
       </c>
-      <c r="B51" s="117">
+      <c r="B51" s="100">
         <v>-431.77489630451402</v>
       </c>
-      <c r="C51" s="117">
+      <c r="C51" s="100">
         <v>20.424589999999998</v>
       </c>
-      <c r="D51" s="117" t="s">
+      <c r="D51" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="E51" s="117" t="s">
+      <c r="E51" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="117" t="s">
+      <c r="F51" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="G51" s="117" t="s">
+      <c r="G51" s="100" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="114">
+      <c r="A52" s="97">
         <v>9</v>
       </c>
-      <c r="B52" s="114">
+      <c r="B52" s="97">
         <v>-444.51806092154101</v>
       </c>
-      <c r="C52" s="114">
+      <c r="C52" s="97">
         <v>0</v>
       </c>
-      <c r="D52" s="114" t="s">
+      <c r="D52" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="E52" s="114" t="s">
+      <c r="E52" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="114" t="s">
+      <c r="F52" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="114" t="s">
+      <c r="G52" s="97" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="117">
+      <c r="A53" s="100">
         <v>7</v>
       </c>
-      <c r="B53" s="117">
+      <c r="B53" s="100">
         <v>-431.77489630451402</v>
       </c>
-      <c r="C53" s="117">
+      <c r="C53" s="100">
         <v>12.74316</v>
       </c>
-      <c r="D53" s="117" t="s">
+      <c r="D53" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="E53" s="117" t="s">
+      <c r="E53" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="117" t="s">
+      <c r="F53" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="G53" s="117" t="s">
+      <c r="G53" s="100" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12146,11 +12113,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FC1287-5697-EF4E-83C4-5EE525DE383D}">
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="108"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -12186,7 +12152,7 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="113">
+      <c r="C2" s="96">
         <v>1.4301390682461801E-43</v>
       </c>
       <c r="D2" t="s">
@@ -12212,7 +12178,7 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="113">
+      <c r="C3" s="96">
         <v>7.6841556884933504E-38</v>
       </c>
       <c r="D3" t="s">
@@ -12238,7 +12204,7 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="113">
+      <c r="C4" s="96">
         <v>4.9089433804905498E-8</v>
       </c>
       <c r="D4" t="s">
@@ -12264,7 +12230,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="113">
+      <c r="C5" s="96">
         <v>4.0950519359541199E-37</v>
       </c>
       <c r="D5" t="s">
@@ -12342,7 +12308,7 @@
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="113">
+      <c r="C8" s="96">
         <v>5.0916100385316105E-7</v>
       </c>
       <c r="D8" t="s">
@@ -12394,7 +12360,7 @@
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="113">
+      <c r="C10" s="96">
         <v>7.7515749872334402E-30</v>
       </c>
       <c r="D10" t="s">
@@ -12420,7 +12386,7 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="113">
+      <c r="C11" s="96">
         <v>1.8059335498504301E-19</v>
       </c>
       <c r="D11" t="s">
@@ -12472,7 +12438,7 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="113">
+      <c r="C13" s="96">
         <v>7.3405227293797297E-25</v>
       </c>
       <c r="D13" t="s">
@@ -12498,7 +12464,7 @@
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="113">
+      <c r="C14" s="96">
         <v>2.3031010347679001E-138</v>
       </c>
       <c r="D14" t="s">
@@ -12524,7 +12490,7 @@
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="113">
+      <c r="C15" s="96">
         <v>1.9912676417461301E-11</v>
       </c>
       <c r="D15" t="s">
@@ -12550,7 +12516,7 @@
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="113">
+      <c r="C16" s="96">
         <v>2.6950923841689601E-17</v>
       </c>
       <c r="D16" t="s">
@@ -12576,7 +12542,7 @@
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="113">
+      <c r="C17" s="96">
         <v>1.46079946252814E-103</v>
       </c>
       <c r="D17" t="s">
@@ -12602,7 +12568,7 @@
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="113">
+      <c r="C18" s="96">
         <v>4.5643333563643598E-11</v>
       </c>
       <c r="D18" t="s">
@@ -12628,7 +12594,7 @@
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="113">
+      <c r="C19" s="96">
         <v>4.1524246376330504E-9</v>
       </c>
       <c r="D19" t="s">
@@ -12654,7 +12620,7 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="113">
+      <c r="C20" s="96">
         <v>3.4380449149797803E-14</v>
       </c>
       <c r="D20" t="s">
@@ -12752,34 +12718,34 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="116">
+      <c r="A24" s="99">
         <v>0.74137157371377505</v>
       </c>
-      <c r="B24" s="116">
+      <c r="B24" s="99">
         <v>2</v>
       </c>
-      <c r="C24" s="116">
+      <c r="C24" s="99">
         <v>0.69026079650210403</v>
       </c>
-      <c r="D24" s="116" t="s">
+      <c r="D24" s="99" t="s">
         <v>249</v>
       </c>
-      <c r="E24" s="116" t="s">
+      <c r="E24" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="116" t="s">
+      <c r="F24" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="G24" s="116" t="s">
+      <c r="G24" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="116" t="s">
+      <c r="H24" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="116" t="s">
+      <c r="I24" s="99" t="s">
         <v>315</v>
       </c>
-      <c r="J24" s="116"/>
+      <c r="J24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
@@ -12807,35 +12773,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="115" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="114">
+    <row r="26" spans="1:10" s="98" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="97">
         <v>13.618280176853199</v>
       </c>
-      <c r="B26" s="114">
+      <c r="B26" s="97">
         <v>3</v>
       </c>
-      <c r="C26" s="118">
+      <c r="C26" s="101">
         <v>3.4735887019868099E-3</v>
       </c>
-      <c r="D26" s="114" t="s">
+      <c r="D26" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="E26" s="114" t="s">
+      <c r="E26" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="114" t="s">
+      <c r="F26" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="114" t="s">
+      <c r="G26" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="114" t="s">
+      <c r="H26" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="I26" s="121" t="s">
+      <c r="I26" s="104" t="s">
         <v>314</v>
       </c>
-      <c r="J26" s="121"/>
+      <c r="J26" s="104"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
@@ -12864,34 +12830,34 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="114">
+      <c r="A28" s="97">
         <v>0.60334988516222698</v>
       </c>
-      <c r="B28" s="114">
+      <c r="B28" s="97">
         <v>2</v>
       </c>
-      <c r="C28" s="114">
+      <c r="C28" s="97">
         <v>0.73957843127691203</v>
       </c>
-      <c r="D28" s="114" t="s">
+      <c r="D28" s="97" t="s">
         <v>252</v>
       </c>
-      <c r="E28" s="114" t="s">
+      <c r="E28" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="114" t="s">
+      <c r="F28" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="114" t="s">
+      <c r="G28" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H28" s="114" t="s">
+      <c r="H28" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="I28" s="121" t="s">
+      <c r="I28" s="104" t="s">
         <v>314</v>
       </c>
-      <c r="J28" s="114"/>
+      <c r="J28" s="97"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
@@ -12972,103 +12938,106 @@
       </c>
     </row>
     <row r="32" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="114">
+      <c r="A32" s="97">
         <v>16.944098479524001</v>
       </c>
-      <c r="B32" s="114">
+      <c r="B32" s="97">
         <v>3</v>
       </c>
-      <c r="C32" s="119">
+      <c r="C32" s="102">
         <v>7.2569982771223502E-4</v>
       </c>
-      <c r="D32" s="114" t="s">
+      <c r="D32" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="114" t="s">
+      <c r="E32" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="114" t="s">
+      <c r="F32" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="114" t="s">
+      <c r="G32" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="114" t="s">
+      <c r="H32" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="121" t="s">
+      <c r="I32" s="104" t="s">
         <v>314</v>
       </c>
-      <c r="J32" s="122"/>
-    </row>
-    <row r="33" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="116">
+      <c r="J32" s="105"/>
+    </row>
+    <row r="33" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="99">
         <v>35.972039821557097</v>
       </c>
-      <c r="B33" s="116">
+      <c r="B33" s="99">
         <v>3</v>
       </c>
-      <c r="C33" s="119">
+      <c r="C33" s="102">
         <v>7.5910024552699206E-8</v>
       </c>
-      <c r="D33" s="116" t="s">
+      <c r="D33" s="99" t="s">
         <v>252</v>
       </c>
-      <c r="E33" s="116" t="s">
+      <c r="E33" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="116" t="s">
+      <c r="F33" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="G33" s="116" t="s">
+      <c r="G33" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="116" t="s">
+      <c r="H33" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="116" t="s">
+      <c r="I33" s="99" t="s">
         <v>315</v>
       </c>
-      <c r="J33" s="116"/>
-    </row>
-    <row r="34" spans="1:10" s="115" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="114">
+      <c r="J33" s="99"/>
+      <c r="K33" s="44" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="98" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="97">
         <v>8.1014926692760607</v>
       </c>
-      <c r="B34" s="114">
+      <c r="B34" s="97">
         <v>3</v>
       </c>
-      <c r="C34" s="118">
+      <c r="C34" s="101">
         <v>4.3960072286452399E-2</v>
       </c>
-      <c r="D34" s="114" t="s">
+      <c r="D34" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="E34" s="114" t="s">
+      <c r="E34" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="114" t="s">
+      <c r="F34" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="114" t="s">
+      <c r="G34" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="114" t="s">
+      <c r="H34" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="I34" s="121" t="s">
+      <c r="I34" s="104" t="s">
         <v>314</v>
       </c>
-      <c r="J34" s="121"/>
-    </row>
-    <row r="35" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J34" s="104"/>
+    </row>
+    <row r="35" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>22.5489428174122</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
-      <c r="C35" s="113">
+      <c r="C35" s="96">
         <v>5.0139420325034099E-5</v>
       </c>
       <c r="D35" t="s">
@@ -13087,37 +13056,37 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="116">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="99">
         <v>2.8941483065276801</v>
       </c>
-      <c r="B36" s="116">
+      <c r="B36" s="99">
         <v>3</v>
       </c>
-      <c r="C36" s="116">
+      <c r="C36" s="99">
         <v>0.40823499285685</v>
       </c>
-      <c r="D36" s="116" t="s">
+      <c r="D36" s="99" t="s">
         <v>252</v>
       </c>
-      <c r="E36" s="116" t="s">
+      <c r="E36" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="116" t="s">
+      <c r="F36" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="116" t="s">
+      <c r="G36" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="H36" s="116" t="s">
+      <c r="H36" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="I36" s="116" t="s">
+      <c r="I36" s="99" t="s">
         <v>315</v>
       </c>
-      <c r="J36" s="116"/>
-    </row>
-    <row r="37" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J36" s="99"/>
+    </row>
+    <row r="37" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>15.474320789891101</v>
       </c>
@@ -13143,37 +13112,37 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="115" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="114">
+    <row r="38" spans="1:11" s="98" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="97">
         <v>27.488711899029699</v>
       </c>
-      <c r="B38" s="114">
+      <c r="B38" s="97">
         <v>3</v>
       </c>
-      <c r="C38" s="119">
+      <c r="C38" s="102">
         <v>4.6498026943556003E-6</v>
       </c>
-      <c r="D38" s="114" t="s">
+      <c r="D38" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="E38" s="114" t="s">
+      <c r="E38" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="114" t="s">
+      <c r="F38" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="G38" s="114" t="s">
+      <c r="G38" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="114" t="s">
+      <c r="H38" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="I38" s="120" t="s">
+      <c r="I38" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="J38" s="121"/>
-    </row>
-    <row r="39" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J38" s="104"/>
+    </row>
+    <row r="39" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>11.1978749798607</v>
       </c>
@@ -13199,7 +13168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6.0915039447393102</v>
       </c>
@@ -13225,7 +13194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8.4354986018774802</v>
       </c>
@@ -13251,37 +13220,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="114">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="97">
         <v>1.78273947658777</v>
       </c>
-      <c r="B42" s="114">
+      <c r="B42" s="97">
         <v>3</v>
       </c>
-      <c r="C42" s="114">
+      <c r="C42" s="97">
         <v>0.61869820311526103</v>
       </c>
-      <c r="D42" s="114" t="s">
+      <c r="D42" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="E42" s="114" t="s">
+      <c r="E42" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="114" t="s">
+      <c r="F42" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="114" t="s">
+      <c r="G42" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="114" t="s">
+      <c r="H42" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="I42" s="120" t="s">
+      <c r="I42" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="J42" s="114"/>
-    </row>
-    <row r="43" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J42" s="97"/>
+    </row>
+    <row r="43" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>13.479413541594001</v>
       </c>
@@ -13307,37 +13276,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="115" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="114">
+    <row r="44" spans="1:11" s="98" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="97">
         <v>17.829165766905199</v>
       </c>
-      <c r="B44" s="114">
+      <c r="B44" s="97">
         <v>3</v>
       </c>
-      <c r="C44" s="118">
+      <c r="C44" s="101">
         <v>4.7701198339367899E-4</v>
       </c>
-      <c r="D44" s="114" t="s">
+      <c r="D44" s="97" t="s">
         <v>252</v>
       </c>
-      <c r="E44" s="114" t="s">
+      <c r="E44" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="114" t="s">
+      <c r="F44" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="114" t="s">
+      <c r="G44" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H44" s="114" t="s">
+      <c r="H44" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="120" t="s">
+      <c r="I44" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="J44" s="121"/>
-    </row>
-    <row r="45" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J44" s="104"/>
+    </row>
+    <row r="45" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>19.402345687276402</v>
       </c>
@@ -13363,7 +13332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1574.1074770783</v>
       </c>
@@ -13389,7 +13358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1566.4145632781799</v>
       </c>
@@ -13415,7 +13384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1563.5457961611401</v>
       </c>
@@ -13474,7 +13443,7 @@
       <c r="B50">
         <v>1</v>
       </c>
-      <c r="C50" s="113">
+      <c r="C50" s="96">
         <v>7.6319193379548197E-37</v>
       </c>
       <c r="D50" t="s">
@@ -13500,7 +13469,7 @@
       <c r="B51">
         <v>1</v>
       </c>
-      <c r="C51" s="113">
+      <c r="C51" s="96">
         <v>6.9692937647008603E-42</v>
       </c>
       <c r="D51" t="s">
@@ -13526,7 +13495,7 @@
       <c r="B52">
         <v>1</v>
       </c>
-      <c r="C52" s="113">
+      <c r="C52" s="96">
         <v>2.8213288615643398E-47</v>
       </c>
       <c r="D52" t="s">
@@ -13552,7 +13521,7 @@
       <c r="B53">
         <v>1</v>
       </c>
-      <c r="C53" s="113">
+      <c r="C53" s="96">
         <v>5.1431841045009798E-42</v>
       </c>
       <c r="D53" t="s">
@@ -13578,7 +13547,7 @@
       <c r="B54">
         <v>1</v>
       </c>
-      <c r="C54" s="113">
+      <c r="C54" s="96">
         <v>1.39728659441433E-6</v>
       </c>
       <c r="D54" t="s">
@@ -13604,7 +13573,7 @@
       <c r="B55">
         <v>1</v>
       </c>
-      <c r="C55" s="113">
+      <c r="C55" s="96">
         <v>8.1087848839048403E-7</v>
       </c>
       <c r="D55" t="s">
@@ -13630,7 +13599,7 @@
       <c r="B56">
         <v>1</v>
       </c>
-      <c r="C56" s="113">
+      <c r="C56" s="96">
         <v>8.1162581861714698E-7</v>
       </c>
       <c r="D56" t="s">
@@ -13656,7 +13625,7 @@
       <c r="B57">
         <v>1</v>
       </c>
-      <c r="C57" s="113">
+      <c r="C57" s="96">
         <v>9.6303045731771293E-7</v>
       </c>
       <c r="D57" t="s">
@@ -13786,7 +13755,7 @@
       <c r="B62">
         <v>1</v>
       </c>
-      <c r="C62" s="113">
+      <c r="C62" s="96">
         <v>6.5922063786487599E-184</v>
       </c>
       <c r="D62" t="s">
@@ -13812,7 +13781,7 @@
       <c r="B63">
         <v>1</v>
       </c>
-      <c r="C63" s="113">
+      <c r="C63" s="96">
         <v>4.4572239371017699E-172</v>
       </c>
       <c r="D63" t="s">
@@ -13838,7 +13807,7 @@
       <c r="B64">
         <v>1</v>
       </c>
-      <c r="C64" s="113">
+      <c r="C64" s="96">
         <v>3.75972011049009E-182</v>
       </c>
       <c r="D64" t="s">
@@ -13864,7 +13833,7 @@
       <c r="B65">
         <v>1</v>
       </c>
-      <c r="C65" s="113">
+      <c r="C65" s="96">
         <v>1.70175402246487E-184</v>
       </c>
       <c r="D65" t="s">
@@ -13890,7 +13859,7 @@
       <c r="B66">
         <v>1</v>
       </c>
-      <c r="C66" s="113">
+      <c r="C66" s="96">
         <v>3.1612613376137499E-291</v>
       </c>
       <c r="D66" t="s">
@@ -13916,7 +13885,7 @@
       <c r="B67">
         <v>1</v>
       </c>
-      <c r="C67" s="113">
+      <c r="C67" s="96">
         <v>5.5139992298651899E-241</v>
       </c>
       <c r="D67" t="s">
@@ -13942,7 +13911,7 @@
       <c r="B68">
         <v>1</v>
       </c>
-      <c r="C68" s="113">
+      <c r="C68" s="96">
         <v>1.89003154193189E-281</v>
       </c>
       <c r="D68" t="s">
@@ -13968,7 +13937,7 @@
       <c r="B69">
         <v>1</v>
       </c>
-      <c r="C69" s="113">
+      <c r="C69" s="96">
         <v>2.9333076958993202E-239</v>
       </c>
       <c r="D69" t="s">
@@ -13994,7 +13963,7 @@
       <c r="B70">
         <v>1</v>
       </c>
-      <c r="C70" s="113">
+      <c r="C70" s="96">
         <v>2.2130735770847701E-227</v>
       </c>
       <c r="D70" t="s">
@@ -14020,7 +13989,7 @@
       <c r="B71">
         <v>1</v>
       </c>
-      <c r="C71" s="113">
+      <c r="C71" s="96">
         <v>1.11442739917519E-206</v>
       </c>
       <c r="D71" t="s">
@@ -14046,7 +14015,7 @@
       <c r="B72">
         <v>1</v>
       </c>
-      <c r="C72" s="113">
+      <c r="C72" s="96">
         <v>1.6473730625626199E-208</v>
       </c>
       <c r="D72" t="s">
@@ -14072,7 +14041,7 @@
       <c r="B73">
         <v>1</v>
       </c>
-      <c r="C73" s="113">
+      <c r="C73" s="96">
         <v>4.1893419212049003E-231</v>
       </c>
       <c r="D73" t="s">
@@ -14098,7 +14067,7 @@
       <c r="B74">
         <v>1</v>
       </c>
-      <c r="C74" s="113">
+      <c r="C74" s="96">
         <v>7.0527413977452401E-185</v>
       </c>
       <c r="D74" t="s">
@@ -14124,7 +14093,7 @@
       <c r="B75">
         <v>1</v>
       </c>
-      <c r="C75" s="113">
+      <c r="C75" s="96">
         <v>1.8958596061434301E-192</v>
       </c>
       <c r="D75" t="s">
@@ -14150,7 +14119,7 @@
       <c r="B76">
         <v>1</v>
       </c>
-      <c r="C76" s="113">
+      <c r="C76" s="96">
         <v>2.7839604230958902E-214</v>
       </c>
       <c r="D76" t="s">
@@ -14176,7 +14145,7 @@
       <c r="B77">
         <v>1</v>
       </c>
-      <c r="C77" s="113">
+      <c r="C77" s="96">
         <v>2.53278556939946E-197</v>
       </c>
       <c r="D77" t="s">
@@ -14202,7 +14171,7 @@
       <c r="B78">
         <v>1</v>
       </c>
-      <c r="C78" s="113">
+      <c r="C78" s="96">
         <v>3.4900934361710001E-16</v>
       </c>
       <c r="D78" t="s">
@@ -14228,7 +14197,7 @@
       <c r="B79">
         <v>1</v>
       </c>
-      <c r="C79" s="113">
+      <c r="C79" s="96">
         <v>1.83455351318415E-16</v>
       </c>
       <c r="D79" t="s">
@@ -14254,7 +14223,7 @@
       <c r="B80">
         <v>1</v>
       </c>
-      <c r="C80" s="113">
+      <c r="C80" s="96">
         <v>2.1897786816690301E-16</v>
       </c>
       <c r="D80" t="s">
@@ -14280,7 +14249,7 @@
       <c r="B81">
         <v>1</v>
       </c>
-      <c r="C81" s="113">
+      <c r="C81" s="96">
         <v>1.4321051718604499E-16</v>
       </c>
       <c r="D81" t="s">
@@ -14306,7 +14275,7 @@
       <c r="B82">
         <v>1</v>
       </c>
-      <c r="C82" s="113">
+      <c r="C82" s="96">
         <v>2.5074683809991999E-5</v>
       </c>
       <c r="D82" t="s">
@@ -14332,7 +14301,7 @@
       <c r="B83">
         <v>1</v>
       </c>
-      <c r="C83" s="113">
+      <c r="C83" s="96">
         <v>2.8969162473161101E-6</v>
       </c>
       <c r="D83" t="s">
@@ -14358,7 +14327,7 @@
       <c r="B84">
         <v>1</v>
       </c>
-      <c r="C84" s="113">
+      <c r="C84" s="96">
         <v>1.4868102926491601E-6</v>
       </c>
       <c r="D84" t="s">
@@ -14384,7 +14353,7 @@
       <c r="B85">
         <v>1</v>
       </c>
-      <c r="C85" s="113">
+      <c r="C85" s="96">
         <v>1.95394460475915E-6</v>
       </c>
       <c r="D85" t="s">
@@ -14410,7 +14379,7 @@
       <c r="B86">
         <v>1</v>
       </c>
-      <c r="C86" s="113">
+      <c r="C86" s="96">
         <v>1.72167515233917E-6</v>
       </c>
       <c r="D86" t="s">
@@ -14436,7 +14405,7 @@
       <c r="B87">
         <v>1</v>
       </c>
-      <c r="C87" s="113">
+      <c r="C87" s="96">
         <v>1.0429890763406999E-6</v>
       </c>
       <c r="D87" t="s">
@@ -14462,7 +14431,7 @@
       <c r="B88">
         <v>1</v>
       </c>
-      <c r="C88" s="113">
+      <c r="C88" s="96">
         <v>1.1254564135199E-6</v>
       </c>
       <c r="D88" t="s">
@@ -14488,7 +14457,7 @@
       <c r="B89">
         <v>1</v>
       </c>
-      <c r="C89" s="113">
+      <c r="C89" s="96">
         <v>1.4233417814482799E-6</v>
       </c>
       <c r="D89" t="s">
@@ -14618,7 +14587,7 @@
       <c r="B94">
         <v>1</v>
       </c>
-      <c r="C94" s="113">
+      <c r="C94" s="96">
         <v>6.8481490190243605E-10</v>
       </c>
       <c r="D94" t="s">
@@ -14644,7 +14613,7 @@
       <c r="B95">
         <v>1</v>
       </c>
-      <c r="C95" s="113">
+      <c r="C95" s="96">
         <v>4.7403544941620701E-12</v>
       </c>
       <c r="D95" t="s">
@@ -14670,7 +14639,7 @@
       <c r="B96">
         <v>1</v>
       </c>
-      <c r="C96" s="113">
+      <c r="C96" s="96">
         <v>1.74554588407026E-13</v>
       </c>
       <c r="D96" t="s">
@@ -14696,7 +14665,7 @@
       <c r="B97">
         <v>1</v>
       </c>
-      <c r="C97" s="113">
+      <c r="C97" s="96">
         <v>2.32900527250289E-12</v>
       </c>
       <c r="D97" t="s">
@@ -14820,34 +14789,34 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A102" s="114">
+      <c r="A102" s="97">
         <v>2.6028170917065601</v>
       </c>
-      <c r="B102" s="114">
+      <c r="B102" s="97">
         <v>4</v>
       </c>
-      <c r="C102" s="114">
+      <c r="C102" s="97">
         <v>0.62632416958747295</v>
       </c>
-      <c r="D102" s="114" t="s">
+      <c r="D102" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="E102" s="114" t="s">
+      <c r="E102" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="F102" s="114" t="s">
+      <c r="F102" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="114" t="s">
+      <c r="G102" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="H102" s="114" t="s">
+      <c r="H102" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="I102" s="121" t="s">
+      <c r="I102" s="104" t="s">
         <v>314</v>
       </c>
-      <c r="J102" s="114"/>
+      <c r="J102" s="97"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103">
@@ -14876,34 +14845,34 @@
       </c>
     </row>
     <row r="104" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="116">
+      <c r="A104" s="99">
         <v>10.117759446015601</v>
       </c>
-      <c r="B104" s="116">
+      <c r="B104" s="99">
         <v>4</v>
       </c>
-      <c r="C104" s="118">
+      <c r="C104" s="101">
         <v>3.8490077267993403E-2</v>
       </c>
-      <c r="D104" s="116" t="s">
+      <c r="D104" s="99" t="s">
         <v>252</v>
       </c>
-      <c r="E104" s="116" t="s">
+      <c r="E104" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="F104" s="116" t="s">
+      <c r="F104" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="G104" s="116" t="s">
+      <c r="G104" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="H104" s="116" t="s">
+      <c r="H104" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="I104" s="116" t="s">
+      <c r="I104" s="99" t="s">
         <v>315</v>
       </c>
-      <c r="J104" s="116"/>
+      <c r="J104" s="99"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105">
@@ -14938,7 +14907,7 @@
       <c r="B106">
         <v>1</v>
       </c>
-      <c r="C106" s="113">
+      <c r="C106" s="96">
         <v>1.9830389729603599E-46</v>
       </c>
       <c r="D106" t="s">
@@ -14964,7 +14933,7 @@
       <c r="B107">
         <v>1</v>
       </c>
-      <c r="C107" s="113">
+      <c r="C107" s="96">
         <v>6.8817454999099197E-46</v>
       </c>
       <c r="D107" t="s">
@@ -14990,7 +14959,7 @@
       <c r="B108">
         <v>1</v>
       </c>
-      <c r="C108" s="113">
+      <c r="C108" s="96">
         <v>5.21594209453367E-45</v>
       </c>
       <c r="D108" t="s">
@@ -15016,7 +14985,7 @@
       <c r="B109">
         <v>1</v>
       </c>
-      <c r="C109" s="113">
+      <c r="C109" s="96">
         <v>2.1451156781821001E-45</v>
       </c>
       <c r="D109" t="s">
@@ -15250,7 +15219,7 @@
       <c r="B118">
         <v>1</v>
       </c>
-      <c r="C118" s="113">
+      <c r="C118" s="96">
         <v>2.4209228003871802E-22</v>
       </c>
       <c r="D118" t="s">
@@ -15276,7 +15245,7 @@
       <c r="B119">
         <v>1</v>
       </c>
-      <c r="C119" s="113">
+      <c r="C119" s="96">
         <v>1.20987773375073E-119</v>
       </c>
       <c r="D119" t="s">
@@ -15302,7 +15271,7 @@
       <c r="B120">
         <v>1</v>
       </c>
-      <c r="C120" s="113">
+      <c r="C120" s="96">
         <v>1.9120675094643899E-49</v>
       </c>
       <c r="D120" t="s">
@@ -15328,7 +15297,7 @@
       <c r="B121">
         <v>1</v>
       </c>
-      <c r="C121" s="113">
+      <c r="C121" s="96">
         <v>1.8719569498258401E-36</v>
       </c>
       <c r="D121" t="s">
@@ -15354,7 +15323,7 @@
       <c r="B122">
         <v>1</v>
       </c>
-      <c r="C122" s="113">
+      <c r="C122" s="96">
         <v>4.3792993619739998E-83</v>
       </c>
       <c r="D122" t="s">
@@ -15380,7 +15349,7 @@
       <c r="B123">
         <v>1</v>
       </c>
-      <c r="C123" s="113">
+      <c r="C123" s="96">
         <v>2.99045792599007E-83</v>
       </c>
       <c r="D123" t="s">
@@ -15406,7 +15375,7 @@
       <c r="B124">
         <v>1</v>
       </c>
-      <c r="C124" s="113">
+      <c r="C124" s="96">
         <v>4.4740962709868497E-84</v>
       </c>
       <c r="D124" t="s">
@@ -15432,7 +15401,7 @@
       <c r="B125">
         <v>1</v>
       </c>
-      <c r="C125" s="113">
+      <c r="C125" s="96">
         <v>3.1468491584487001E-83</v>
       </c>
       <c r="D125" t="s">
@@ -15562,7 +15531,7 @@
       <c r="B130">
         <v>1</v>
       </c>
-      <c r="C130" s="113">
+      <c r="C130" s="96">
         <v>6.1984650932245597E-113</v>
       </c>
       <c r="D130" t="s">
@@ -15588,7 +15557,7 @@
       <c r="B131">
         <v>1</v>
       </c>
-      <c r="C131" s="113">
+      <c r="C131" s="96">
         <v>2.02541005453363E-111</v>
       </c>
       <c r="D131" t="s">
@@ -15614,7 +15583,7 @@
       <c r="B132">
         <v>1</v>
       </c>
-      <c r="C132" s="113">
+      <c r="C132" s="96">
         <v>3.0800439980529902E-109</v>
       </c>
       <c r="D132" t="s">
@@ -15640,7 +15609,7 @@
       <c r="B133">
         <v>1</v>
       </c>
-      <c r="C133" s="113">
+      <c r="C133" s="96">
         <v>3.9780146875797601E-112</v>
       </c>
       <c r="D133" t="s">
@@ -15666,7 +15635,7 @@
       <c r="B134">
         <v>1</v>
       </c>
-      <c r="C134" s="113">
+      <c r="C134" s="96">
         <v>5.1232837862335003E-17</v>
       </c>
       <c r="D134" t="s">
@@ -15692,7 +15661,7 @@
       <c r="B135">
         <v>1</v>
       </c>
-      <c r="C135" s="113">
+      <c r="C135" s="96">
         <v>1.2112581353884599E-14</v>
       </c>
       <c r="D135" t="s">
@@ -15718,7 +15687,7 @@
       <c r="B136">
         <v>1</v>
       </c>
-      <c r="C136" s="113">
+      <c r="C136" s="96">
         <v>5.3233303187281703E-20</v>
       </c>
       <c r="D136" t="s">
@@ -15744,7 +15713,7 @@
       <c r="B137">
         <v>1</v>
       </c>
-      <c r="C137" s="113">
+      <c r="C137" s="96">
         <v>4.9614735258530897E-16</v>
       </c>
       <c r="D137" t="s">
@@ -15794,10 +15763,10 @@
       <c r="F1" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="I1" s="137">
+      <c r="I1" s="120">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J1" s="137">
+      <c r="J1" s="120">
         <v>0.97499999999999998</v>
       </c>
       <c r="K1" t="s">
@@ -18175,13 +18144,13 @@
       <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="137" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="130" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="32" t="s">
@@ -18204,9 +18173,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="100"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="97"/>
+      <c r="A3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="131"/>
       <c r="D3" s="33" t="s">
         <v>49</v>
       </c>
@@ -18231,9 +18200,9 @@
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="97"/>
+      <c r="A4" s="134"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="131"/>
       <c r="D4" s="35" t="s">
         <v>62</v>
       </c>
@@ -18260,13 +18229,13 @@
       </c>
     </row>
     <row r="5" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="100" t="s">
+      <c r="A5" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="131" t="s">
         <v>63</v>
       </c>
       <c r="D5" s="36" t="s">
@@ -18293,9 +18262,9 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="97"/>
+      <c r="A6" s="134"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="131"/>
       <c r="D6" s="33" t="s">
         <v>6</v>
       </c>
@@ -18320,9 +18289,9 @@
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="101"/>
-      <c r="C7" s="97"/>
+      <c r="A7" s="134"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="131"/>
       <c r="D7" s="35" t="s">
         <v>62</v>
       </c>
@@ -18347,13 +18316,13 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="134" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="97"/>
+      <c r="C8" s="131"/>
       <c r="D8" s="36" t="s">
         <v>50</v>
       </c>
@@ -18371,9 +18340,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="100"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="97"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="131"/>
       <c r="D9" s="33" t="s">
         <v>6</v>
       </c>
@@ -18391,9 +18360,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="97"/>
+      <c r="A10" s="134"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="131"/>
       <c r="D10" s="35" t="s">
         <v>62</v>
       </c>
@@ -18411,11 +18380,11 @@
       </c>
     </row>
     <row r="11" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="97"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="131"/>
       <c r="D11" s="36" t="s">
         <v>50</v>
       </c>
@@ -18433,9 +18402,9 @@
       </c>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="97"/>
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="131"/>
       <c r="D12" s="33" t="s">
         <v>6</v>
       </c>
@@ -18453,9 +18422,9 @@
       </c>
     </row>
     <row r="13" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="97"/>
+      <c r="A13" s="134"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="131"/>
       <c r="D13" s="35" t="s">
         <v>62</v>
       </c>
@@ -18473,11 +18442,11 @@
       </c>
     </row>
     <row r="14" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="97"/>
+      <c r="B14" s="135"/>
+      <c r="C14" s="131"/>
       <c r="D14" s="36" t="s">
         <v>50</v>
       </c>
@@ -18495,9 +18464,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="100"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="97"/>
+      <c r="A15" s="134"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="131"/>
       <c r="D15" s="33" t="s">
         <v>6</v>
       </c>
@@ -18515,9 +18484,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="100"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="97"/>
+      <c r="A16" s="134"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="131"/>
       <c r="D16" s="35" t="s">
         <v>62</v>
       </c>
@@ -18535,11 +18504,11 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="101"/>
-      <c r="C17" s="97"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="131"/>
       <c r="D17" s="36" t="s">
         <v>50</v>
       </c>
@@ -18557,9 +18526,9 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="97"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="131"/>
       <c r="D18" s="33" t="s">
         <v>6</v>
       </c>
@@ -18577,9 +18546,9 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="97"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="35" t="s">
         <v>62</v>
       </c>
@@ -18597,13 +18566,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="134" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="101" t="s">
+      <c r="B20" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="97"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="36" t="s">
         <v>50</v>
       </c>
@@ -18621,9 +18590,9 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="100"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="97"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="33" t="s">
         <v>6</v>
       </c>
@@ -18641,9 +18610,9 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="100"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="97"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="33" t="s">
         <v>62</v>
       </c>
@@ -18661,9 +18630,9 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="100"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="97"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="37" t="s">
         <v>14</v>
       </c>
@@ -18681,11 +18650,11 @@
       </c>
     </row>
     <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="100" t="s">
+      <c r="A24" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="97"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="131"/>
       <c r="D24" s="32" t="s">
         <v>50</v>
       </c>
@@ -18703,9 +18672,9 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="100"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="97"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="135"/>
+      <c r="C25" s="131"/>
       <c r="D25" s="33" t="s">
         <v>6</v>
       </c>
@@ -18723,9 +18692,9 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="100"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="97"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="135"/>
+      <c r="C26" s="131"/>
       <c r="D26" s="34" t="s">
         <v>62</v>
       </c>
@@ -18743,9 +18712,9 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="100"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="97"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="135"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="35" t="s">
         <v>14</v>
       </c>
@@ -18763,11 +18732,11 @@
       </c>
     </row>
     <row r="28" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="97"/>
+      <c r="B28" s="135"/>
+      <c r="C28" s="131"/>
       <c r="D28" s="32" t="s">
         <v>50</v>
       </c>
@@ -18785,9 +18754,9 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="100"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="97"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="135"/>
+      <c r="C29" s="131"/>
       <c r="D29" s="33" t="s">
         <v>6</v>
       </c>
@@ -18805,9 +18774,9 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="100"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="97"/>
+      <c r="A30" s="134"/>
+      <c r="B30" s="135"/>
+      <c r="C30" s="131"/>
       <c r="D30" s="33" t="s">
         <v>62</v>
       </c>
@@ -18825,9 +18794,9 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="100"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="97"/>
+      <c r="A31" s="134"/>
+      <c r="B31" s="135"/>
+      <c r="C31" s="131"/>
       <c r="D31" s="35" t="s">
         <v>14</v>
       </c>
@@ -18845,11 +18814,11 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="100" t="s">
+      <c r="A32" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="101"/>
-      <c r="C32" s="97"/>
+      <c r="B32" s="135"/>
+      <c r="C32" s="131"/>
       <c r="D32" s="32" t="s">
         <v>50</v>
       </c>
@@ -18867,9 +18836,9 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="100"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="97"/>
+      <c r="A33" s="134"/>
+      <c r="B33" s="135"/>
+      <c r="C33" s="131"/>
       <c r="D33" s="33" t="s">
         <v>6</v>
       </c>
@@ -18887,9 +18856,9 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="100"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="97"/>
+      <c r="A34" s="134"/>
+      <c r="B34" s="135"/>
+      <c r="C34" s="131"/>
       <c r="D34" s="33" t="s">
         <v>62</v>
       </c>
@@ -18907,9 +18876,9 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="104"/>
-      <c r="B35" s="102"/>
-      <c r="C35" s="98"/>
+      <c r="A35" s="138"/>
+      <c r="B35" s="136"/>
+      <c r="C35" s="132"/>
       <c r="D35" s="35" t="s">
         <v>14</v>
       </c>
